--- a/outputs/147-48.xlsx
+++ b/outputs/147-48.xlsx
@@ -149,8 +149,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -350,148 +354,148 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
     </row>
